--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -469,10 +469,10 @@
         <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Nella</v>
+        <v>Britney</v>
       </c>
       <c r="C2" t="str">
-        <v>Miller</v>
+        <v>Schmidt</v>
       </c>
       <c r="D2" t="str">
         <v>14343</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>6388668189</v>
+        <v>1304500672</v>
       </c>
       <c r="N2" t="str">
-        <v>nella@yopmail.com</v>
+        <v>britney@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>

--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -469,10 +469,10 @@
         <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Britney</v>
+        <v>Irwin</v>
       </c>
       <c r="C2" t="str">
-        <v>Schmidt</v>
+        <v>Stokes</v>
       </c>
       <c r="D2" t="str">
         <v>14343</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>1304500672</v>
+        <v>1529045895</v>
       </c>
       <c r="N2" t="str">
-        <v>britney@yopmail.com</v>
+        <v>irwin@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>

--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -469,13 +469,13 @@
         <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Irwin</v>
+        <v>Napoleon</v>
       </c>
       <c r="C2" t="str">
-        <v>Stokes</v>
+        <v>Marvin</v>
       </c>
       <c r="D2" t="str">
-        <v>14343</v>
+        <v>13911</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>1529045895</v>
+        <v>2413825109</v>
       </c>
       <c r="N2" t="str">
-        <v>irwin@yopmail.com</v>
+        <v>napoleon@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>

--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>FOS</v>
       </c>
       <c r="B2" t="str">
-        <v>Napoleon</v>
+        <v>Noelia</v>
       </c>
       <c r="C2" t="str">
-        <v>Marvin</v>
+        <v>Schoen</v>
       </c>
       <c r="D2" t="str">
         <v>13911</v>
@@ -484,13 +484,13 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>23577359447</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>Agency Frontend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>2413825109</v>
+        <v>7345382183</v>
       </c>
       <c r="N2" t="str">
-        <v>napoleon@yopmail.com</v>
+        <v>noelia@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>re35sr</v>
+        <v>resr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOS</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Noelia</v>
+        <v>Lia</v>
       </c>
       <c r="C2" t="str">
-        <v>Schoen</v>
+        <v>Medhurst</v>
       </c>
       <c r="D2" t="str">
         <v>13911</v>
@@ -484,13 +484,13 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>23577359447</v>
       </c>
       <c r="J2" t="str">
         <v>Agency Frontend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>7345382183</v>
+        <v>5895434061</v>
       </c>
       <c r="N2" t="str">
-        <v>noelia@yopmail.com</v>
+        <v>lia@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>resr</v>
+        <v>re35sr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -1,44 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Encollect_Project\Web_Testing\SCB\Frameworks\SCB\March_Release_SCB\Cypress\fixtures\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CD8C33-475E-4DC2-A8BF-9DE54BE601FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+  <si>
+    <t>UserType</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>AgencyCode</t>
+  </si>
+  <si>
+    <t>SupervisorEmailId</t>
+  </si>
+  <si>
+    <t>DialerId</t>
+  </si>
+  <si>
+    <t>DRACertificationDate</t>
+  </si>
+  <si>
+    <t>DRATrainingDate</t>
+  </si>
+  <si>
+    <t>DRAUniqueRegistrationNumber</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>MobileNo</t>
+  </si>
+  <si>
+    <t>EmailId</t>
+  </si>
+  <si>
+    <t>FathersName</t>
+  </si>
+  <si>
+    <t>LocalResidentialAddress</t>
+  </si>
+  <si>
+    <t>PostalCode</t>
+  </si>
+  <si>
+    <t>CollectionEmploymentDate</t>
+  </si>
+  <si>
+    <t>LastRenewalDate</t>
+  </si>
+  <si>
+    <t>AuthorizationCardExpiryDate</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>FOS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agency Frontend</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>18-10-1979</t>
+  </si>
+  <si>
+    <t>yop</t>
+  </si>
+  <si>
+    <t>bakori</t>
+  </si>
+  <si>
+    <t>765523</t>
+  </si>
+  <si>
+    <t>19-10-2022</t>
+  </si>
+  <si>
+    <t>19-10-2023</t>
+  </si>
+  <si>
+    <t>10-10-2033</t>
+  </si>
+  <si>
+    <t>resr</t>
+  </si>
+  <si>
+    <t>Tyree</t>
+  </si>
+  <si>
+    <t>Rechert</t>
+  </si>
+  <si>
+    <t>tyrse@yopmail.com</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -61,17 +168,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,143 +514,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="23.375" customWidth="1"/>
+    <col min="7" max="7" width="17.625" customWidth="1"/>
+    <col min="8" max="8" width="16.375" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="13" max="13" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.75" customWidth="1"/>
+    <col min="18" max="18" width="14.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>UserType</v>
-      </c>
-      <c r="B1" t="str">
-        <v>FirstName</v>
-      </c>
-      <c r="C1" t="str">
-        <v>LastName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>AgencyCode</v>
-      </c>
-      <c r="E1" t="str">
-        <v>SupervisorEmailId</v>
-      </c>
-      <c r="F1" t="str">
-        <v>DialerId</v>
-      </c>
-      <c r="G1" t="str">
-        <v>DRACertificationDate</v>
-      </c>
-      <c r="H1" t="str">
-        <v>DRATrainingDate</v>
-      </c>
-      <c r="I1" t="str">
-        <v>DRAUniqueRegistrationNumber</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Department</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Designation</v>
-      </c>
-      <c r="L1" t="str">
-        <v>DateOfBirth</v>
-      </c>
-      <c r="M1" t="str">
-        <v>MobileNo</v>
-      </c>
-      <c r="N1" t="str">
-        <v>EmailId</v>
-      </c>
-      <c r="O1" t="str">
-        <v>FathersName</v>
-      </c>
-      <c r="P1" t="str">
-        <v>LocalResidentialAddress</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>PostalCode</v>
-      </c>
-      <c r="R1" t="str">
-        <v>CollectionEmploymentDate</v>
-      </c>
-      <c r="S1" t="str">
-        <v>LastRenewalDate</v>
-      </c>
-      <c r="T1" t="str">
-        <v>AuthorizationCardExpiryDate</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Remarks</v>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Telecaller</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Lia</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Medhurst</v>
-      </c>
-      <c r="D2" t="str">
-        <v>13911</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v>435454</v>
-      </c>
-      <c r="G2" t="str">
-        <v>10-10-2020</v>
-      </c>
-      <c r="H2" t="str">
-        <v>10-10-2020</v>
-      </c>
-      <c r="I2" t="str">
-        <v>23577359447</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Agency Frontend</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Agent</v>
-      </c>
-      <c r="L2" t="str">
-        <v>18-10-1979</v>
-      </c>
-      <c r="M2" t="str">
-        <v>5895434061</v>
-      </c>
-      <c r="N2" t="str">
-        <v>lia@yopmail.com</v>
-      </c>
-      <c r="O2" t="str">
-        <v>yop</v>
-      </c>
-      <c r="P2" t="str">
-        <v>bakori</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>765523</v>
-      </c>
-      <c r="R2" t="str">
-        <v>19-10-2022</v>
-      </c>
-      <c r="S2" t="str">
-        <v>19-10-2023</v>
-      </c>
-      <c r="T2" t="str">
-        <v>10-10-2033</v>
-      </c>
-      <c r="U2" t="str">
-        <v>re35sr</v>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2">
+        <v>17657</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>675453</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>2792597696</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{DBBD0C18-7228-4C81-8BF0-14D9153E9AC5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U2"/>
+    <ignoredError sqref="A1:U1 A2 E2 G2:L2 O2:U2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>